--- a/Sajjad data/by_country_and_state/USA/NV.xlsx
+++ b/Sajjad data/by_country_and_state/USA/NV.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="268">
   <si>
     <t>Business Name</t>
   </si>
@@ -782,6 +782,39 @@
   </si>
   <si>
     <t>2026-10-25T09:48:46.378Z</t>
+  </si>
+  <si>
+    <t>Dunay Kelley DDS</t>
+  </si>
+  <si>
+    <t>(775) 358-4600</t>
+  </si>
+  <si>
+    <t>685 E Prater Way, Sparks, NV 89431</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dunay+Kelley+DDS/data=!4m7!3m6!1s0x80993ed0ede9910d:0x4c0ddaf7b64e9b7c!8m2!3d39.5413638!4d-119.7342171!16s%2Fg%2F113h7wh59!19sChIJDZHp7dA-mYARfJtOtvfaDUw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:08.969Z</t>
+  </si>
+  <si>
+    <t>Morgan Mark R DDS</t>
+  </si>
+  <si>
+    <t>(775) 827-3746</t>
+  </si>
+  <si>
+    <t>1155 W 4th St #218, Reno, NV 89503</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Morgan+Mark+R+DDS/data=!4m7!3m6!1s0x8099472c074b4323:0x7714286fcb33560f!8m2!3d39.5263869!4d-119.8291717!16s%2Fg%2F1tgpbjdf!19sChIJI0NLByxHmYARD1Yzy28oFHc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:41:47.815Z</t>
   </si>
 </sst>
 </file>
@@ -1162,7 +1195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2860,6 +2893,88 @@
         <v>256</v>
       </c>
     </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>257</v>
+      </c>
+      <c r="B42" t="s">
+        <v>258</v>
+      </c>
+      <c r="C42" t="s">
+        <v>191</v>
+      </c>
+      <c r="D42" t="s">
+        <v>259</v>
+      </c>
+      <c r="E42" t="s">
+        <v>233</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>49</v>
+      </c>
+      <c r="I42" t="s">
+        <v>88</v>
+      </c>
+      <c r="J42" t="s">
+        <v>49</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>260</v>
+      </c>
+      <c r="M42" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>262</v>
+      </c>
+      <c r="B43" t="s">
+        <v>263</v>
+      </c>
+      <c r="C43" t="s">
+        <v>213</v>
+      </c>
+      <c r="D43" t="s">
+        <v>264</v>
+      </c>
+      <c r="E43" t="s">
+        <v>169</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>49</v>
+      </c>
+      <c r="I43" t="s">
+        <v>265</v>
+      </c>
+      <c r="J43" t="s">
+        <v>49</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>266</v>
+      </c>
+      <c r="M43" t="s">
+        <v>267</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
